--- a/r4-ELGA-e-Medikation-ig-review/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-ig-review/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T05:47:45+00:00</t>
+    <t>2026-07-13T07:18:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-ig-review/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-ig-review/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:18:56+00:00</t>
+    <t>2026-07-13T07:30:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-ig-review/CodeSystem-MedicationRequestCategoryCS.xlsx
+++ b/r4-ELGA-e-Medikation-ig-review/CodeSystem-MedicationRequestCategoryCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:30:44+00:00</t>
+    <t>2026-07-13T07:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
